--- a/Libraries/Vehicle/Steer/Rack/sm_car_data_Steer_Rack_Wheel_Indep.xlsx
+++ b/Libraries/Vehicle/Steer/Rack/sm_car_data_Steer_Rack_Wheel_Indep.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Steer\Rack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC1AD6B-DF49-429E-868A-67D56F4A96A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1AC9F9-95F3-41EC-9885-EF1FA1DA222E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2415" yWindow="1590" windowWidth="17625" windowHeight="11865" tabRatio="940" activeTab="3" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
+    <workbookView xWindow="3030" yWindow="1605" windowWidth="21600" windowHeight="11295" tabRatio="940" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
   </bookViews>
   <sheets>
     <sheet name="RWheel_Hamba_f" sheetId="7" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="30">
   <si>
     <t>Units</t>
   </si>
@@ -121,6 +121,12 @@
   </si>
   <si>
     <t>RackWheelIndep_SUV_Landy_f</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>N/(m/s)</t>
   </si>
 </sst>
 </file>
@@ -230,7 +236,63 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -661,7 +723,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="13" customWidth="1"/>
@@ -800,130 +862,138 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="11">
-        <v>-1.0213531220517</v>
-      </c>
-      <c r="G9" s="11">
-        <v>0.37675517503754502</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
       <c r="H9" s="11">
-        <v>0.92326153885340301</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="B10" s="5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
+        <v>11</v>
+      </c>
+      <c r="F10" s="11">
+        <v>-1.0213531220517</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0.37675517503754502</v>
+      </c>
       <c r="H10" s="11">
-        <v>0.35289999999999999</v>
+        <v>0.92326153885340301</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11">
-        <v>1</v>
+        <v>0.35289999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
-      <c r="H14" s="11"/>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
+      <c r="H15" s="11"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H16" s="11"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
+      <c r="H17" s="11"/>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
+      <c r="K21" s="15"/>
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
     </row>
@@ -931,12 +1001,10 @@
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B23" s="13"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -949,49 +1017,68 @@
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B25" s="13"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B27" s="13"/>
-      <c r="H27" s="14"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B28" s="13"/>
       <c r="H28" s="14"/>
     </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B29" s="13"/>
+      <c r="H29" s="14"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A27:A28">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B12">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:B26">
-    <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E12">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+  <conditionalFormatting sqref="A28:A29">
+    <cfRule type="cellIs" dxfId="23" priority="8" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:B7 A9:B13">
+    <cfRule type="cellIs" dxfId="22" priority="4" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A24:B27">
+    <cfRule type="cellIs" dxfId="21" priority="10" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5 E7 E9:E13">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1004,7 +1091,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="13" customWidth="1"/>
@@ -1143,109 +1230,119 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="6">
-        <v>-1.3243331220516996</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0.45175517503754498</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0.88921153885340298</v>
+        <v>17</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="B10" s="5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11">
-        <v>0.35289999999999999</v>
+        <v>11</v>
+      </c>
+      <c r="F10" s="6">
+        <v>-1.3243331220516996</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.45175517503754498</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0.88921153885340298</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11">
-        <v>1</v>
+        <v>0.35289999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
-      <c r="H14" s="11"/>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
+      <c r="H15" s="11"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H16" s="11"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
+      <c r="H17" s="11"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F19" s="6"/>
@@ -1268,7 +1365,6 @@
       <c r="H22" s="6"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="13"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -1280,6 +1376,7 @@
       <c r="H24" s="6"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="13"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -1290,31 +1387,46 @@
       <c r="H26" s="6"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="13"/>
-      <c r="H27" s="14"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="13"/>
       <c r="H28" s="14"/>
     </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="13"/>
+      <c r="H29" s="14"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A27:A28">
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B12">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:B26">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E12">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+  <conditionalFormatting sqref="A28:A29">
+    <cfRule type="cellIs" dxfId="17" priority="6" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:B7 A9:B13">
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A24:B27">
+    <cfRule type="cellIs" dxfId="15" priority="8" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5 E7 E9:E13">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1327,7 +1439,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="13" customWidth="1"/>
@@ -1466,88 +1578,98 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="11">
-        <v>1.18</v>
-      </c>
-      <c r="G9" s="11">
-        <v>0.55926517503754503</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
       <c r="H9" s="11">
-        <v>1.34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="B10" s="5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
+        <v>11</v>
+      </c>
+      <c r="F10" s="11">
+        <v>1.18</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0.55926517503754503</v>
+      </c>
       <c r="H10" s="11">
-        <v>0.78888879999999995</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11">
-        <v>1</v>
+        <v>0.78888879999999995</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F14" s="6"/>
@@ -1557,12 +1679,12 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="11"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="11"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F18" s="6"/>
@@ -1590,7 +1712,6 @@
       <c r="H22" s="6"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="13"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -1602,6 +1723,7 @@
       <c r="H24" s="6"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="13"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -1612,31 +1734,46 @@
       <c r="H26" s="6"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="13"/>
-      <c r="H27" s="14"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="13"/>
       <c r="H28" s="14"/>
     </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="13"/>
+      <c r="H29" s="14"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A27:A28">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B12">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:B26">
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E12">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+  <conditionalFormatting sqref="A28:A29">
+    <cfRule type="cellIs" dxfId="11" priority="8" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:B7 A9:B13">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A24:B27">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5 E7 E9:E13">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1649,7 +1786,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="13" customWidth="1"/>
@@ -1789,109 +1926,119 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="15">
-        <v>-1.0213531220517</v>
-      </c>
-      <c r="G9" s="15">
-        <v>-0.37675517503754502</v>
-      </c>
-      <c r="H9" s="15">
-        <v>1.2232615388534001</v>
+        <v>17</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="B10" s="5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11">
-        <v>0.35289999999999999</v>
+        <v>11</v>
+      </c>
+      <c r="F10" s="15">
+        <v>-1.0213531220517</v>
+      </c>
+      <c r="G10" s="15">
+        <v>-0.37675517503754502</v>
+      </c>
+      <c r="H10" s="15">
+        <v>1.2232615388534001</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11">
-        <v>1</v>
+        <v>0.35289999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
-      <c r="H14" s="11"/>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
+      <c r="H15" s="11"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H16" s="11"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
+      <c r="H17" s="11"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F19" s="6"/>
@@ -1914,7 +2061,6 @@
       <c r="H22" s="6"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="13"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -1926,6 +2072,7 @@
       <c r="H24" s="6"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="13"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -1936,31 +2083,46 @@
       <c r="H26" s="6"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="13"/>
-      <c r="H27" s="14"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="13"/>
       <c r="H28" s="14"/>
     </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="13"/>
+      <c r="H29" s="14"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A27:A28">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B12">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:B26">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E12">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="A28:A29">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:B7 A9:B13">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A24:B27">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5 E7 E9:E13">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
